--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2496-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2496-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C1CBAFBB-C6EC-4D9A-BCEF-C202E4F42177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{081E6FE2-12E2-496D-AA48-E3BCCE736C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{427EE1FD-3AE4-46ED-A270-9960B350AEA6}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F3D29E29-A42B-4CFC-88BB-FDA38E04DCAC}"/>
   </bookViews>
   <sheets>
     <sheet name="2496-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1502,28 +1502,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{672362B9-EA25-4B9D-9788-8321C6115947}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E25440A-0C1C-4BEE-AC26-BB633FBD438B}">
   <dimension ref="A1:X35"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1557,7 +1557,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1593,7 +1593,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1713,7 +1713,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1859,7 +1859,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1931,7 +1931,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="36">
         <v>2023</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2022</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2021</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2020</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>9.42</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2018</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>6.51</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2017</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2016</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>3.26</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="42"/>
       <c r="B16" s="43"/>
       <c r="C16" s="19" t="s">
@@ -2535,7 +2535,7 @@
       <c r="W16" s="49"/>
       <c r="X16" s="45"/>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2015</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2014</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2013</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2012</v>
       </c>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2011</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2010</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2009</v>
       </c>
@@ -3039,7 +3039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2008</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2007</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2006</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2005</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2004</v>
       </c>
@@ -3399,7 +3399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2003</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2002</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>2001</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2000</v>
       </c>
@@ -3687,7 +3687,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>1999</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>1998</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36" t="s">
         <v>44</v>
       </c>
